--- a/data/trans_camb/IP2001-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP2001-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 7,45</t>
+          <t>-3,48; 6,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 11,88</t>
+          <t>-0,77; 12,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 6,47</t>
+          <t>-2,73; 6,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,22; -0,92</t>
+          <t>-10,21; -0,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 9,31</t>
+          <t>-3,87; 10,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 4,21</t>
+          <t>-7,17; 4,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 2,03</t>
+          <t>-5,15; 1,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 8,32</t>
+          <t>-0,45; 8,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 4,14</t>
+          <t>-3,24; 4,3</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-62,78; 622,2</t>
+          <t>-73,87; 439,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,29; 999,06</t>
+          <t>-33,44; 897,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-55,56; 452,69</t>
+          <t>-57,94; 423,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 48,83</t>
+          <t>-100,0; 39,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-48,97; 277,75</t>
+          <t>-46,03; 309,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-69,83; 146,68</t>
+          <t>-67,6; 148,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-74,46; 84,16</t>
+          <t>-76,43; 64,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,52; 280,03</t>
+          <t>-14,96; 266,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-45,0; 126,52</t>
+          <t>-44,28; 146,86</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 10,35</t>
+          <t>-2,13; 10,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 10,19</t>
+          <t>-1,69; 9,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 1,6</t>
+          <t>-8,15; 1,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 2,76</t>
+          <t>-8,68; 2,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 6,4</t>
+          <t>-5,64; 6,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 6,43</t>
+          <t>-6,64; 6,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 5,24</t>
+          <t>-3,65; 4,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 6,52</t>
+          <t>-2,17; 6,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 2,66</t>
+          <t>-5,01; 2,58</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-57,19; 653,8</t>
+          <t>-46,33; 808,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-35,75; 931,39</t>
+          <t>-36,18; 665,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1014,32 +1014,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-77,72; 103,51</t>
+          <t>-83,75; 84,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-58,28; 183,74</t>
+          <t>-57,71; 195,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,17; 163,86</t>
+          <t>-70,28; 194,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-48,06; 185,98</t>
+          <t>-52,52; 152,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,7; 216,34</t>
+          <t>-30,86; 190,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-72,59; 99,14</t>
+          <t>-71,95; 90,06</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 12,04</t>
+          <t>-4,39; 12,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 6,97</t>
+          <t>-9,29; 6,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 7,65</t>
+          <t>-9,56; 7,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 12,15</t>
+          <t>0,01; 12,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 6,9</t>
+          <t>-3,93; 7,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 1,63</t>
+          <t>-7,28; 1,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 10,32</t>
+          <t>0,35; 9,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 4,69</t>
+          <t>-4,18; 4,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 2,43</t>
+          <t>-6,34; 1,92</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-37,17; 283,16</t>
+          <t>-38,61; 257,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-69,67; 176,47</t>
+          <t>-72,24; 153,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-76,4; 190,86</t>
+          <t>-78,47; 203,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,62; 539,94</t>
+          <t>-13,2; 507,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-68,01; 319,86</t>
+          <t>-70,58; 348,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 195,41</t>
+          <t>-100,0; 217,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,38; 254,64</t>
+          <t>-1,67; 233,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-54,34; 118,74</t>
+          <t>-54,15; 114,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-76,18; 75,84</t>
+          <t>-76,34; 53,82</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 5,49</t>
+          <t>-4,44; 5,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 9,37</t>
+          <t>-0,4; 9,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 0,29</t>
+          <t>-8,5; 0,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 2,18</t>
+          <t>-6,87; 2,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 5,4</t>
+          <t>-4,77; 5,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 1,92</t>
+          <t>-8,04; 2,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 2,23</t>
+          <t>-4,54; 2,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 5,91</t>
+          <t>-1,82; 5,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,83; -0,44</t>
+          <t>-6,87; -0,1</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-40,57; 83,26</t>
+          <t>-38,97; 77,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 145,15</t>
+          <t>-3,85; 135,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-73,41; 5,93</t>
+          <t>-71,69; 9,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-55,58; 34,69</t>
+          <t>-54,64; 35,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-38,63; 73,84</t>
+          <t>-36,86; 64,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-61,88; 26,43</t>
+          <t>-61,95; 28,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-40,62; 28,53</t>
+          <t>-39,48; 31,88</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 71,16</t>
+          <t>-16,1; 66,14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-60,44; -4,8</t>
+          <t>-59,63; 1,61</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 8,04</t>
+          <t>-6,11; 8,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 7,1</t>
+          <t>-7,24; 7,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,16; -2,26</t>
+          <t>-14,27; -1,9</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 11,57</t>
+          <t>-2,3; 11,77</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 12,6</t>
+          <t>-1,03; 13,8</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 0,82</t>
+          <t>-10,28; 0,95</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 8,29</t>
+          <t>-1,58; 7,92</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 8,17</t>
+          <t>-1,41; 7,83</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-10,33; -1,64</t>
+          <t>-10,15; -1,58</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-36,33; 102,04</t>
+          <t>-38,77; 97,03</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-44,75; 88,63</t>
+          <t>-45,36; 89,1</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-85,9; -13,04</t>
+          <t>-86,21; -14,09</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 157,79</t>
+          <t>-18,69; 160,43</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 167,29</t>
+          <t>-8,55; 183,2</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-73,38; 22,47</t>
+          <t>-75,53; 17,02</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 98,24</t>
+          <t>-12,78; 88,5</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 93,49</t>
+          <t>-11,61; 87,92</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-73,87; -13,11</t>
+          <t>-73,26; -14,3</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 3,45</t>
+          <t>-7,23; 3,37</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 7,99</t>
+          <t>-4,58; 7,67</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 1,76</t>
+          <t>-7,62; 2,1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4,2; 18,57</t>
+          <t>3,28; 18,21</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 4,94</t>
+          <t>-3,16; 5,26</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 8,75</t>
+          <t>-2,32; 9,39</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,49; 10,61</t>
+          <t>0,33; 10,3</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 4,73</t>
+          <t>-2,86; 4,73</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 4,17</t>
+          <t>-3,95; 3,83</t>
         </is>
       </c>
     </row>
@@ -1868,42 +1868,42 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-72,72; 459,66</t>
+          <t>-73,8; 378,92</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 293,29</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>0,0; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>16,73; —</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 565,35</t>
+          <t>-6,89; 685,19</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-60,59; 264,5</t>
+          <t>-60,07; 319,98</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-74,72; 255,01</t>
+          <t>-82,14; 255,31</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 4,34</t>
+          <t>-0,83; 4,43</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,41; 5,62</t>
+          <t>0,47; 5,82</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,19; -0,94</t>
+          <t>-5,19; -0,85</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 3,57</t>
+          <t>-1,33; 3,76</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 4,66</t>
+          <t>-0,46; 4,51</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 0,4</t>
+          <t>-4,16; 0,3</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 3,38</t>
+          <t>-0,4; 3,26</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,57</t>
+          <t>0,91; 4,39</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,0; -0,93</t>
+          <t>-4,24; -0,95</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 70,58</t>
+          <t>-9,41; 71,33</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>4,97; 93,39</t>
+          <t>4,72; 92,68</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-60,79; -15,02</t>
+          <t>-60,63; -12,33</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 55,83</t>
+          <t>-15,77; 58,57</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 74,25</t>
+          <t>-5,29; 68,92</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-47,7; 6,34</t>
+          <t>-47,56; 5,35</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 49,45</t>
+          <t>-4,59; 47,76</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>9,07; 67,87</t>
+          <t>8,42; 61,62</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-48,25; -14,05</t>
+          <t>-50,2; -13,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2001-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP2001-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 6,33</t>
+          <t>-3,41; 6,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 12,23</t>
+          <t>-0,88; 11,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 6,42</t>
+          <t>-2,77; 6,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,21; -0,22</t>
+          <t>-10,03; -0,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 10,14</t>
+          <t>-3,59; 8,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 4,27</t>
+          <t>-6,88; 4,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 1,62</t>
+          <t>-4,79; 1,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 8,63</t>
+          <t>-0,65; 8,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 4,3</t>
+          <t>-3,14; 3,99</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-73,87; 439,38</t>
+          <t>-68,43; 433,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-33,44; 897,03</t>
+          <t>-35,94; 767,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-57,94; 423,85</t>
+          <t>-53,74; 354,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 39,13</t>
+          <t>-100,0; 56,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,03; 309,28</t>
+          <t>-46,02; 256,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,6; 148,05</t>
+          <t>-69,32; 131,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-76,43; 64,6</t>
+          <t>-73,92; 64,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-14,96; 266,43</t>
+          <t>-12,74; 265,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-44,28; 146,86</t>
+          <t>-46,06; 132,21</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 10,23</t>
+          <t>-2,04; 10,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 9,39</t>
+          <t>-1,34; 9,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 1,25</t>
+          <t>-7,33; 1,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 2,43</t>
+          <t>-8,34; 3,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 6,19</t>
+          <t>-5,73; 6,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 6,13</t>
+          <t>-6,39; 7,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 4,69</t>
+          <t>-3,51; 4,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 6,3</t>
+          <t>-2,08; 6,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 2,58</t>
+          <t>-5,16; 2,6</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-46,33; 808,2</t>
+          <t>-53,86; 686,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-36,18; 665,03</t>
+          <t>-35,41; 757,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1014,32 +1014,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-83,75; 84,73</t>
+          <t>-81,95; 102,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,71; 195,27</t>
+          <t>-58,81; 163,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-70,28; 194,41</t>
+          <t>-67,52; 250,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-52,52; 152,23</t>
+          <t>-49,5; 151,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,86; 190,75</t>
+          <t>-28,63; 209,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-71,95; 90,06</t>
+          <t>-72,5; 94,45</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 12,47</t>
+          <t>-4,4; 13,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 6,18</t>
+          <t>-9,33; 6,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 7,75</t>
+          <t>-9,33; 6,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 12,42</t>
+          <t>-0,35; 11,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 7,41</t>
+          <t>-3,46; 8,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 1,65</t>
+          <t>-7,4; 2,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 9,97</t>
+          <t>0,17; 10,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 4,85</t>
+          <t>-4,16; 5,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 1,92</t>
+          <t>-6,44; 2,41</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,61; 257,4</t>
+          <t>-38,05; 284,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-72,24; 153,56</t>
+          <t>-74,33; 135,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-78,47; 203,28</t>
+          <t>-72,66; 181,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 507,57</t>
+          <t>-14,1; 465,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-70,58; 348,88</t>
+          <t>-58,93; 410,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 217,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 233,23</t>
+          <t>-0,74; 267,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-54,15; 114,48</t>
+          <t>-51,76; 132,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-76,34; 53,82</t>
+          <t>-75,33; 63,6</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 5,04</t>
+          <t>-4,56; 4,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 9,15</t>
+          <t>-0,72; 9,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 0,15</t>
+          <t>-8,51; 0,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 2,51</t>
+          <t>-7,51; 2,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 5,44</t>
+          <t>-4,7; 5,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 2,25</t>
+          <t>-8,11; 1,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 2,47</t>
+          <t>-4,5; 2,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 5,48</t>
+          <t>-0,91; 6,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,87; -0,1</t>
+          <t>-6,94; -0,28</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-38,97; 77,54</t>
+          <t>-40,33; 70,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 135,51</t>
+          <t>-9,4; 135,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-71,69; 9,02</t>
+          <t>-73,08; 5,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-54,64; 35,44</t>
+          <t>-56,71; 34,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-36,86; 64,92</t>
+          <t>-37,09; 66,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-61,95; 28,82</t>
+          <t>-62,18; 22,84</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-39,48; 31,88</t>
+          <t>-39,12; 31,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-16,1; 66,14</t>
+          <t>-8,36; 81,4</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-59,63; 1,61</t>
+          <t>-60,51; -3,58</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 8,23</t>
+          <t>-5,9; 8,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 7,4</t>
+          <t>-7,1; 6,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,27; -1,9</t>
+          <t>-14,23; -1,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 11,77</t>
+          <t>-2,11; 11,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 13,8</t>
+          <t>-1,18; 12,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 0,95</t>
+          <t>-10,87; 0,88</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 7,92</t>
+          <t>-1,84; 8,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 7,83</t>
+          <t>-2,38; 7,77</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-10,15; -1,58</t>
+          <t>-10,4; -1,79</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-38,77; 97,03</t>
+          <t>-36,29; 97,18</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-45,36; 89,1</t>
+          <t>-43,65; 88,61</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-86,21; -14,09</t>
+          <t>-86,55; -13,65</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-18,69; 160,43</t>
+          <t>-18,79; 158,64</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 183,2</t>
+          <t>-12,04; 163,05</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-75,53; 17,02</t>
+          <t>-74,88; 18,7</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,78; 88,5</t>
+          <t>-14,44; 89,58</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 87,92</t>
+          <t>-18,2; 91,86</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-73,26; -14,3</t>
+          <t>-74,45; -16,36</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 3,37</t>
+          <t>-7,2; 4,02</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 7,67</t>
+          <t>-4,91; 7,09</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 2,1</t>
+          <t>-7,77; 1,94</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,28; 18,21</t>
+          <t>3,97; 18,03</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 5,26</t>
+          <t>-3,01; 5,79</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 9,39</t>
+          <t>-2,37; 8,68</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,33; 10,3</t>
+          <t>0,46; 10,75</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 4,73</t>
+          <t>-2,96; 4,9</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 3,83</t>
+          <t>-3,86; 3,79</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 327,45</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>-75,23; 421,14</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 300,97</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>16,11; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>-73,8; 378,92</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 293,29</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>0,0; —</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 685,19</t>
+          <t>-14,02; 559,77</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-60,07; 319,98</t>
+          <t>-61,8; 290,84</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-82,14; 255,31</t>
+          <t>-79,72; 269,75</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 4,43</t>
+          <t>-0,58; 4,37</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,47; 5,82</t>
+          <t>0,35; 5,66</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,19; -0,85</t>
+          <t>-5,6; -1,02</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 3,76</t>
+          <t>-1,38; 3,54</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 4,51</t>
+          <t>-0,31; 4,76</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 0,3</t>
+          <t>-4,21; 0,71</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 3,26</t>
+          <t>-0,28; 3,38</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,39</t>
+          <t>0,95; 4,35</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,24; -0,95</t>
+          <t>-4,08; -0,81</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 71,33</t>
+          <t>-7,75; 70,53</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>4,72; 92,68</t>
+          <t>3,72; 93,67</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-60,63; -12,33</t>
+          <t>-62,53; -14,0</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-15,77; 58,57</t>
+          <t>-15,41; 54,18</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 68,92</t>
+          <t>-3,49; 75,46</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-47,56; 5,35</t>
+          <t>-48,1; 11,46</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 47,76</t>
+          <t>-3,04; 51,46</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>8,42; 61,62</t>
+          <t>11,87; 65,1</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-50,2; -13,04</t>
+          <t>-49,15; -12,03</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2001-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP2001-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-4,75</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,31</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-0,75</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1,32</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>4,58</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,94</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-4,75</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,31</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,9</t>
+          <t>1,73</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,53</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 6,37</t>
+          <t>-10,22; -0,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 11,42</t>
+          <t>-4,13; 9,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 6,4</t>
+          <t>-6,66; 4,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,03; -0,18</t>
+          <t>-3,08; 7,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 8,89</t>
+          <t>-1,02; 11,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 4,42</t>
+          <t>-3,17; 6,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 1,87</t>
+          <t>-4,87; 2,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 8,11</t>
+          <t>-0,79; 8,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 3,99</t>
+          <t>-3,01; 4,15</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-74,91%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>36,44%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-11,86%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>36,19%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>125,92%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53,46%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-74,91%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>36,44%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-14,21%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-68,43; 433,94</t>
+          <t>-100,0; 48,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-35,94; 767,92</t>
+          <t>-48,97; 277,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-53,74; 354,71</t>
+          <t>-68,6; 160,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 56,56</t>
+          <t>-62,78; 622,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,02; 256,11</t>
+          <t>-30,29; 999,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-69,32; 131,72</t>
+          <t>-58,32; 420,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-73,92; 64,19</t>
+          <t>-74,46; 84,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 265,2</t>
+          <t>-18,52; 280,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-46,06; 132,21</t>
+          <t>-44,96; 135,28</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-2,39</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,61</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-0,02</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3,95</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>4,17</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,18</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,39</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,61</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>-2,33</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,32</t>
+          <t>-1,28</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 10,02</t>
+          <t>-8,2; 2,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 9,73</t>
+          <t>-5,39; 6,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 1,32</t>
+          <t>-6,37; 7,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 3,01</t>
+          <t>-2,17; 10,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 6,12</t>
+          <t>-1,35; 10,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 7,23</t>
+          <t>-7,09; 1,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 4,72</t>
+          <t>-3,35; 5,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 6,5</t>
+          <t>-1,74; 6,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 2,6</t>
+          <t>-4,91; 2,62</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-36,16%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9,22%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-0,29%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>106,71%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>112,65%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-58,92%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-36,16%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,22%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-5,97%</t>
+          <t>-62,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-25,53%</t>
+          <t>-24,86%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-53,86; 686,01</t>
+          <t>-77,72; 103,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-35,41; 757,41</t>
+          <t>-58,28; 183,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>-66,41; 173,86</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>-57,19; 653,8</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>-35,75; 931,39</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-81,95; 102,88</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-58,81; 163,05</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-67,52; 250,05</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,5; 151,29</t>
+          <t>-48,06; 185,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-28,63; 209,11</t>
+          <t>-26,7; 216,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-72,5; 94,45</t>
+          <t>-71,79; 105,27</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,03</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,14</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-2,94</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>4,15</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-1,22</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,3</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,03</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,14</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-3,13</t>
+          <t>-1,79</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,13</t>
+          <t>-2,06</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 13,02</t>
+          <t>-0,52; 12,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 6,51</t>
+          <t>-4,39; 6,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 6,97</t>
+          <t>-6,97; 2,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 11,17</t>
+          <t>-4,09; 12,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 8,03</t>
+          <t>-8,9; 6,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 2,31</t>
+          <t>-9,92; 6,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 10,32</t>
+          <t>0,34; 10,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 5,14</t>
+          <t>-4,11; 4,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 2,41</t>
+          <t>-5,97; 2,63</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>108,26%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>24,47%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-63,34%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>48,32%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-14,18%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-15,11%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>108,26%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>24,47%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-67,43%</t>
+          <t>-20,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-34,37%</t>
+          <t>-33,23%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,05; 284,05</t>
+          <t>-17,62; 539,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-74,33; 135,34</t>
+          <t>-68,01; 319,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-72,66; 181,31</t>
+          <t>-100,0; 230,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 465,19</t>
+          <t>-37,17; 283,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-58,93; 410,79</t>
+          <t>-69,67; 176,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-80,27; 167,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 267,61</t>
+          <t>1,38; 254,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-51,76; 132,22</t>
+          <t>-54,34; 118,74</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-75,33; 63,6</t>
+          <t>-77,04; 81,13</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-2,49</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,27</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-2,89</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,05</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>4,26</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-4,15</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-2,49</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,27</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,1</t>
+          <t>-2,95</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-3,62</t>
+          <t>-2,87</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 4,83</t>
+          <t>-7,26; 2,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 9,2</t>
+          <t>-4,87; 5,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 0,29</t>
+          <t>-8,01; 2,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 2,39</t>
+          <t>-4,66; 5,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 5,1</t>
+          <t>-0,73; 9,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 1,36</t>
+          <t>-7,37; 1,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 2,57</t>
+          <t>-4,43; 2,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 6,24</t>
+          <t>-1,45; 5,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,94; -0,28</t>
+          <t>-6,04; 0,53</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-23,96%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-27,75%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>0,55%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>46,52%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-45,27%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-23,96%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-29,77%</t>
+          <t>-32,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-37,05%</t>
+          <t>-29,39%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-40,33; 70,66</t>
+          <t>-55,58; 34,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 135,11</t>
+          <t>-38,63; 73,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-73,08; 5,47</t>
+          <t>-60,73; 31,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-56,71; 34,6</t>
+          <t>-40,57; 83,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-37,09; 66,91</t>
+          <t>-6,82; 145,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-62,18; 22,84</t>
+          <t>-64,2; 28,84</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-39,12; 31,73</t>
+          <t>-40,62; 28,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 81,4</t>
+          <t>-13,1; 71,16</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-60,51; -3,58</t>
+          <t>-53,74; 7,19</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4,75</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5,92</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-4,2</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>1,3</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,34</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-7,71</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4,75</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>5,92</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-4,52</t>
+          <t>-7,44</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-5,91</t>
+          <t>-5,65</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 8,07</t>
+          <t>-1,92; 11,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 6,97</t>
+          <t>-0,49; 12,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,23; -1,62</t>
+          <t>-10,35; 1,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 11,28</t>
+          <t>-5,7; 8,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 12,73</t>
+          <t>-7,27; 7,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 0,88</t>
+          <t>-13,97; -1,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 8,14</t>
+          <t>-1,87; 8,29</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 7,77</t>
+          <t>-1,88; 8,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-10,4; -1,79</t>
+          <t>-10,07; -1,18</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>45,05%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>56,18%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-39,8%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>10,8%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>2,86%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-64,24%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>45,05%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>56,18%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-42,85%</t>
+          <t>-62,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-52,77%</t>
+          <t>-50,45%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-36,29; 97,18</t>
+          <t>-16,17; 157,79</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-43,65; 88,61</t>
+          <t>-7,8; 167,29</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-86,55; -13,65</t>
+          <t>-72,02; 30,34</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-18,79; 158,64</t>
+          <t>-36,33; 102,04</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 163,05</t>
+          <t>-44,75; 88,63</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-74,88; 18,7</t>
+          <t>-85,11; -8,58</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 89,58</t>
+          <t>-13,17; 98,24</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-18,2; 91,86</t>
+          <t>-13,52; 93,49</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-74,45; -16,36</t>
+          <t>-72,46; -9,37</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>10,58</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0,95</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1,37</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-1,87</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1,01</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-2,64</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>10,58</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>0,95</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,09</t>
+          <t>-2,58</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,33</t>
+          <t>-0,68</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 4,02</t>
+          <t>4,2; 18,57</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 7,09</t>
+          <t>-3,13; 4,94</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 1,94</t>
+          <t>-3,03; 6,38</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,97; 18,03</t>
+          <t>-7,51; 3,45</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 5,79</t>
+          <t>-4,34; 7,99</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 8,68</t>
+          <t>-7,72; 1,95</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,46; 10,75</t>
+          <t>0,49; 10,61</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 4,9</t>
+          <t>-3,13; 4,73</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 3,79</t>
+          <t>-3,73; 3,18</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>529,85%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>47,71%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>68,55%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-40,47%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>21,97%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-57,29%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>529,85%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>47,71%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>104,46%</t>
+          <t>-55,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-9,8%</t>
+          <t>-20,28%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 327,45</t>
+          <t>16,73; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-75,23; 421,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 300,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>16,11; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
+          <t>-72,72; 459,66</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 559,77</t>
+          <t>-5,57; 565,35</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-61,8; 290,84</t>
+          <t>-60,59; 264,5</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-79,72; 269,75</t>
+          <t>-78,07; 205,09</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>1,14</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2,12</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-1,73</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>1,85</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>3,01</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-3,1</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1,14</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>2,12</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-1,9</t>
+          <t>-2,85</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-2,46</t>
+          <t>-2,26</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 4,37</t>
+          <t>-1,48; 3,57</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,35; 5,66</t>
+          <t>-0,56; 4,66</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,6; -1,02</t>
+          <t>-4,09; 0,51</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 3,54</t>
+          <t>-0,6; 4,34</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 4,76</t>
+          <t>0,41; 5,62</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 0,71</t>
+          <t>-4,91; -0,62</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 3,38</t>
+          <t>-0,21; 3,38</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,35</t>
+          <t>0,79; 4,57</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,08; -0,81</t>
+          <t>-3,86; -0,69</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>14,88%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>27,76%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-22,72%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>24,91%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>40,65%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-41,82%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>14,88%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>27,76%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-24,86%</t>
+          <t>-38,44%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-32,66%</t>
+          <t>-30,06%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 70,53</t>
+          <t>-17,18; 55,83</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3,72; 93,67</t>
+          <t>-7,19; 74,25</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-62,53; -14,0</t>
+          <t>-45,83; 9,05</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-15,41; 54,18</t>
+          <t>-6,94; 70,58</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 75,46</t>
+          <t>4,97; 93,39</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-48,1; 11,46</t>
+          <t>-57,51; -7,76</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 51,46</t>
+          <t>-3,02; 49,45</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>11,87; 65,1</t>
+          <t>9,07; 67,87</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-49,15; -12,03</t>
+          <t>-45,84; -9,87</t>
         </is>
       </c>
     </row>
